--- a/追蹤矩陣.xlsx
+++ b/追蹤矩陣.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
   <si>
     <t>專案階段</t>
   </si>
@@ -78,58 +78,105 @@
     <t>整理追蹤矩陣</t>
   </si>
   <si>
+    <t>未開始</t>
+  </si>
+  <si>
+    <t>開發</t>
+  </si>
+  <si>
+    <t>程式編寫-前端</t>
+  </si>
+  <si>
+    <t>程式編寫-後端</t>
+  </si>
+  <si>
+    <t>測試</t>
+  </si>
+  <si>
+    <t>單元測試</t>
+  </si>
+  <si>
+    <t>整合測試</t>
+  </si>
+  <si>
+    <t>部署</t>
+  </si>
+  <si>
+    <t>部署到測試環境</t>
+  </si>
+  <si>
+    <t>部署到生產環境</t>
+  </si>
+  <si>
+    <t>維護</t>
+  </si>
+  <si>
+    <t>系統監控</t>
+  </si>
+  <si>
+    <t>問題修復</t>
+  </si>
+  <si>
+    <t>進行中</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具租賃系統-專案追蹤矩陣</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>架構設計</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料結構設計</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能模組規劃</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>界面和流程設計</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>設計</t>
-  </si>
-  <si>
-    <t>系統架構設計</t>
-  </si>
-  <si>
-    <t>2024/OO/OO</t>
-  </si>
-  <si>
-    <t>未開始</t>
-  </si>
-  <si>
-    <t>詳細設計</t>
-  </si>
-  <si>
-    <t>開發</t>
-  </si>
-  <si>
-    <t>程式編寫-前端</t>
-  </si>
-  <si>
-    <t>程式編寫-後端</t>
-  </si>
-  <si>
-    <t>測試</t>
-  </si>
-  <si>
-    <t>單元測試</t>
-  </si>
-  <si>
-    <t>整合測試</t>
-  </si>
-  <si>
-    <t>部署</t>
-  </si>
-  <si>
-    <t>部署到測試環境</t>
-  </si>
-  <si>
-    <t>部署到生產環境</t>
-  </si>
-  <si>
-    <t>維護</t>
-  </si>
-  <si>
-    <t>系統監控</t>
-  </si>
-  <si>
-    <t>問題修復</t>
-  </si>
-  <si>
-    <t>家具租賃系統-專案追蹤矩陣</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>確定系統的整體結構和各模組之間的互動</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>定義數據庫結構、資料流，設計主要資料表和欄位。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大致定義各主要功能模組如何協同運作，哪些需求會對應到哪些功能。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>繪製基本的界面草圖或流程圖，但不進行具體開發。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024/00/00</t>
+  </si>
+  <si>
+    <t>2024/00/00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024/00/00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>已完成</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -168,7 +215,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,6 +225,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF3300"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00CC66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFFF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -290,14 +373,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -310,12 +387,21 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -326,21 +412,69 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -348,6 +482,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCFFFF"/>
+      <color rgb="FF00CC66"/>
+      <color rgb="FFFF3300"/>
+      <color rgb="FF66FF33"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -622,11 +764,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" customWidth="1"/>
     <col min="3" max="3" width="10.28515625" customWidth="1"/>
     <col min="4" max="4" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="16.140625" customWidth="1"/>
@@ -634,495 +776,557 @@
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="25.28515625" customWidth="1"/>
+    <col min="10" max="10" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="11">
+        <v>45548</v>
+      </c>
+      <c r="E3" s="11">
+        <v>45566</v>
+      </c>
+      <c r="F3" s="11">
+        <v>45569</v>
+      </c>
+      <c r="G3" s="11">
+        <v>45569</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="10"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="11">
+        <v>45569</v>
+      </c>
+      <c r="E6" s="11">
+        <v>45571</v>
+      </c>
+      <c r="F6" s="11">
+        <v>45569</v>
+      </c>
+      <c r="G6" s="11">
+        <v>45571</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="17"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="17"/>
+      <c r="B9" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="3">
+        <v>45589</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3">
+        <v>45591</v>
+      </c>
+      <c r="E10" s="3">
+        <v>45592</v>
+      </c>
+      <c r="F10" s="3">
+        <v>45591</v>
+      </c>
+      <c r="G10" s="3">
+        <v>45592</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3">
+        <v>45595</v>
+      </c>
+      <c r="E11" s="3">
+        <v>45596</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="28"/>
+      <c r="B12" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="3">
+        <v>45595</v>
+      </c>
+      <c r="E12" s="3">
+        <v>45596</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="28"/>
+      <c r="B13" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-    </row>
-    <row r="2" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="C13" s="2"/>
+      <c r="D13" s="3">
+        <v>45595</v>
+      </c>
+      <c r="E13" s="3">
+        <v>45596</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="4">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="10">
-        <v>45548</v>
-      </c>
-      <c r="E3" s="10">
-        <v>45566</v>
-      </c>
-      <c r="F3" s="10">
-        <v>45569</v>
-      </c>
-      <c r="G3" s="10">
-        <v>45569</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="13">
-        <v>1</v>
-      </c>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="9"/>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="10">
-        <v>45569</v>
-      </c>
-      <c r="E6" s="10">
-        <v>45571</v>
-      </c>
-      <c r="F6" s="10">
-        <v>45569</v>
-      </c>
-      <c r="G6" s="10">
-        <v>45571</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="13">
-        <v>1</v>
-      </c>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="7"/>
-    </row>
-    <row r="8" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="5">
-        <v>45589</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="6">
-        <v>1</v>
-      </c>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="J13" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="29"/>
+      <c r="B14" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="3">
+        <v>45595</v>
+      </c>
+      <c r="E14" s="3">
+        <v>45596</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3">
         <v>45591</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E15" s="3">
         <v>45592</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="3">
         <v>45591</v>
       </c>
-      <c r="G10" s="5">
+      <c r="E16" s="3">
         <v>45592</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="F16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="6">
+      <c r="I16" s="4">
         <v>0</v>
       </c>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="4" t="s">
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="6">
+      <c r="B17" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3">
+        <v>45591</v>
+      </c>
+      <c r="E17" s="3">
+        <v>45592</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="4">
         <v>0</v>
       </c>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="30"/>
+      <c r="B18" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="6">
+      <c r="C18" s="2"/>
+      <c r="D18" s="3">
+        <v>45591</v>
+      </c>
+      <c r="E18" s="3">
+        <v>45592</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="4">
         <v>0</v>
       </c>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="4" t="s">
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="6">
+      <c r="B19" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="3">
+        <v>45591</v>
+      </c>
+      <c r="E19" s="3">
+        <v>45592</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="4">
         <v>0</v>
       </c>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="30"/>
+      <c r="B20" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="6">
+      <c r="C20" s="2"/>
+      <c r="D20" s="3">
+        <v>45591</v>
+      </c>
+      <c r="E20" s="3">
+        <v>45592</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="4">
         <v>0</v>
       </c>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="4" t="s">
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="6">
+      <c r="B21" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="3">
+        <v>45591</v>
+      </c>
+      <c r="E21" s="3">
+        <v>45592</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="4">
         <v>0</v>
       </c>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="30"/>
+      <c r="B22" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="6">
+      <c r="C22" s="2"/>
+      <c r="D22" s="3">
+        <v>45591</v>
+      </c>
+      <c r="E22" s="3">
+        <v>45592</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="4">
         <v>0</v>
       </c>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="6">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="6">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="6">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4"/>
+      <c r="J22" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A21:A22"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="I6:I8"/>
     <mergeCell ref="J6:J8"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B6:B8"/>
@@ -1133,13 +1337,13 @@
     <mergeCell ref="H6:H8"/>
     <mergeCell ref="A3:A10"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="J3:J5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="F3:F5"/>
     <mergeCell ref="G3:G5"/>
     <mergeCell ref="H3:H5"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="J3:J5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/追蹤矩陣.xlsx
+++ b/追蹤矩陣.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20415"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAA5570-E68B-4EC4-8CE3-5531B0E32B2E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16320" windowHeight="7500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16320" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="56">
   <si>
     <t>專案階段</t>
   </si>
@@ -82,18 +81,9 @@
     <t>開發</t>
   </si>
   <si>
-    <t>程式編寫-前端</t>
-  </si>
-  <si>
-    <t>程式編寫-後端</t>
-  </si>
-  <si>
     <t>測試</t>
   </si>
   <si>
-    <t>單元測試</t>
-  </si>
-  <si>
     <t>整合測試</t>
   </si>
   <si>
@@ -179,13 +169,57 @@
   </si>
   <si>
     <t>郭丞睿</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理者介面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>倉儲管理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物流安排</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>撰寫測試計畫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>撰寫測試報告</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>列出具體的測試場景，包括測試步驟、預期結果和測試數據。這些用例涵蓋了系統的所有功能需求，並可以追溯至需求文件。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>測資生成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>撰寫缺陷報告</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>測試結束後的總結文件，記錄測試的結果、測試通過率、發現的缺陷和改進建議。這份報告用來評估系統是否達到預期質量標準。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>當測試過程中發現錯誤或缺陷時，記錄具體的錯誤描述、重現步驟、影響範圍和優先級，以便開發團隊修正。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述測試的範疇、目標、測試策略、測試環境和資源需求。這份文件為整個測試階段提供了方向和規範。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -375,7 +409,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -408,6 +442,70 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -416,65 +514,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -765,8 +808,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J22"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -782,18 +825,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
+      <c r="A1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
     </row>
     <row r="2" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
@@ -828,126 +871,126 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="20" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="28">
+        <v>44</v>
+      </c>
+      <c r="D3" s="23">
         <v>45548</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="23">
         <v>45566</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="23">
         <v>45569</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="23">
         <v>45569</v>
       </c>
-      <c r="H3" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="18">
+      <c r="H3" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="14">
         <v>1</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="17"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34"/>
-      <c r="B4" s="26"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="21"/>
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="22"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34"/>
-      <c r="B5" s="27"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="23"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="19"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="29"/>
+      <c r="B6" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="28">
+        <v>44</v>
+      </c>
+      <c r="D6" s="23">
         <v>45569</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="23">
         <v>45571</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="23">
         <v>45569</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="23">
         <v>45571</v>
       </c>
-      <c r="H6" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="I6" s="18">
+      <c r="H6" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="14">
         <v>1</v>
       </c>
-      <c r="J6" s="21"/>
+      <c r="J6" s="17"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="21"/>
       <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="22"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34"/>
-      <c r="B8" s="27"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="22"/>
       <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="23"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="19"/>
     </row>
     <row r="9" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="34"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D9" s="3">
         <v>45582</v>
@@ -970,7 +1013,7 @@
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
+      <c r="A10" s="30"/>
       <c r="B10" s="10" t="s">
         <v>17</v>
       </c>
@@ -990,7 +1033,7 @@
         <v>45592</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I10" s="4">
         <v>0.6</v>
@@ -998,11 +1041,11 @@
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
-        <v>37</v>
+      <c r="A11" s="31" t="s">
+        <v>34</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="3">
@@ -1012,10 +1055,10 @@
         <v>45596</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>18</v>
@@ -1024,13 +1067,13 @@
         <v>0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
+      <c r="A12" s="34"/>
       <c r="B12" s="10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="3">
@@ -1040,10 +1083,10 @@
         <v>45596</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>18</v>
@@ -1052,13 +1095,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="3">
@@ -1068,10 +1111,10 @@
         <v>45596</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>18</v>
@@ -1080,13 +1123,13 @@
         <v>0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="3">
@@ -1096,10 +1139,10 @@
         <v>45596</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>18</v>
@@ -1108,15 +1151,15 @@
         <v>0</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="31" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="3">
@@ -1126,10 +1169,10 @@
         <v>45592</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>18</v>
@@ -1140,9 +1183,9 @@
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="10" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="3">
@@ -1152,10 +1195,10 @@
         <v>45592</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>18</v>
@@ -1166,11 +1209,9 @@
       <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
-        <v>22</v>
-      </c>
+      <c r="A17" s="33"/>
       <c r="B17" s="10" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="3">
@@ -1180,10 +1221,10 @@
         <v>45592</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>18</v>
@@ -1193,23 +1234,27 @@
       </c>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
+    <row r="18" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>20</v>
+      </c>
       <c r="B18" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="D18" s="3">
-        <v>45591</v>
+        <v>45606</v>
       </c>
       <c r="E18" s="3">
-        <v>45592</v>
+        <v>45607</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>18</v>
@@ -1217,27 +1262,29 @@
       <c r="I18" s="4">
         <v>0</v>
       </c>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
-        <v>25</v>
-      </c>
+      <c r="J18" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="36"/>
       <c r="B19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="D19" s="3">
-        <v>45591</v>
+        <v>45606</v>
       </c>
       <c r="E19" s="3">
-        <v>45592</v>
+        <v>45607</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>18</v>
@@ -1245,105 +1292,189 @@
       <c r="I19" s="4">
         <v>0</v>
       </c>
-      <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
+      <c r="J19" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="36"/>
       <c r="B20" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="3">
-        <v>45591</v>
-      </c>
-      <c r="E20" s="3">
-        <v>45592</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>42</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
       <c r="H20" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I20" s="4">
         <v>0</v>
       </c>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
-        <v>28</v>
-      </c>
+      <c r="J20" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="36"/>
       <c r="B21" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="3">
-        <v>45591</v>
-      </c>
-      <c r="E21" s="3">
-        <v>45592</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>42</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
       <c r="H21" s="7" t="s">
         <v>18</v>
       </c>
       <c r="I21" s="4">
         <v>0</v>
       </c>
-      <c r="J21" s="2"/>
+      <c r="J21" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15"/>
+      <c r="A22" s="37"/>
       <c r="B22" s="10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="3">
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="3">
         <v>45591</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E23" s="3">
         <v>45592</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" s="7" t="s">
+      <c r="F23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I22" s="4">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2"/>
+      <c r="I23" s="4">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="37"/>
+      <c r="B24" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="3">
+        <v>45591</v>
+      </c>
+      <c r="E24" s="3">
+        <v>45592</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="3">
+        <v>45591</v>
+      </c>
+      <c r="E25" s="3">
+        <v>45592</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="37"/>
+      <c r="B26" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="3">
+        <v>45591</v>
+      </c>
+      <c r="E26" s="3">
+        <v>45592</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="4">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A25:A26"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="F3:F5"/>
     <mergeCell ref="G3:G5"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A19:A20"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="I6:I8"/>
     <mergeCell ref="J6:J8"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A18"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
@@ -1352,6 +1483,10 @@
     <mergeCell ref="H6:H8"/>
     <mergeCell ref="A3:A10"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="D3:D5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
